--- a/artfynd/A 23246-2023 artfynd.xlsx
+++ b/artfynd/A 23246-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23246-2023 artfynd.xlsx
+++ b/artfynd/A 23246-2023 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>112182866</v>
       </c>
       <c r="B4" t="n">
-        <v>96692</v>
+        <v>98092</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594860</v>
+        <v>594861</v>
       </c>
       <c r="R4" t="n">
         <v>6821121</v>

--- a/artfynd/A 23246-2023 artfynd.xlsx
+++ b/artfynd/A 23246-2023 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>112182866</v>
       </c>
       <c r="B4" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 23246-2023 artfynd.xlsx
+++ b/artfynd/A 23246-2023 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>112182866</v>
       </c>
       <c r="B4" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 23246-2023 artfynd.xlsx
+++ b/artfynd/A 23246-2023 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>112182866</v>
       </c>
       <c r="B4" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 23246-2023 artfynd.xlsx
+++ b/artfynd/A 23246-2023 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>112182866</v>
       </c>
       <c r="B4" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,11 +914,6 @@
       </c>
       <c r="E4" t="n">
         <v>219790</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 23246-2023 artfynd.xlsx
+++ b/artfynd/A 23246-2023 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>112182866</v>
       </c>
       <c r="B4" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,6 +914,11 @@
       </c>
       <c r="E4" t="n">
         <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 23246-2023 artfynd.xlsx
+++ b/artfynd/A 23246-2023 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>112182866</v>
       </c>
       <c r="B4" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 23246-2023 artfynd.xlsx
+++ b/artfynd/A 23246-2023 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>112182866</v>
       </c>
       <c r="B4" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 23246-2023 artfynd.xlsx
+++ b/artfynd/A 23246-2023 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>112182866</v>
       </c>
       <c r="B4" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 23246-2023 artfynd.xlsx
+++ b/artfynd/A 23246-2023 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>112182866</v>
       </c>
       <c r="B4" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
